--- a/inputs/tandem_params_new.xlsx
+++ b/inputs/tandem_params_new.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hmdni\OneDrive\Documents\GitHub\odias\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE86D5D-BB4C-4B0C-AB93-59D0B486C72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C25131D-67A4-4CA3-82F4-D29D10DB3090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JUN&amp;AUG24_LOW_VS_HIGH_AGGLOM" sheetId="8" r:id="rId1"/>
+    <sheet name="JUN24-AUG24-FEB25-All" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>fname</t>
   </si>
@@ -167,12 +167,6 @@
     <t>28 Aug. 24</t>
   </si>
   <si>
-    <t>Low agglom.</t>
-  </si>
-  <si>
-    <t>High agglom.</t>
-  </si>
-  <si>
     <t>28AUG24_HIGHAGGLOM_TANDEM_02-Jan-2025_20-23-55</t>
   </si>
   <si>
@@ -183,16 +177,82 @@
   </si>
   <si>
     <t>30JUL24_HIGHAGGLOM_TANDEM_03-Jan-2025_17-02-49</t>
+  </si>
+  <si>
+    <t>Mod-Colaps</t>
+  </si>
+  <si>
+    <t>Lo-Aglom</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>#8174A0</t>
+  </si>
+  <si>
+    <t>mrksz</t>
+  </si>
+  <si>
+    <t>06 Feb. 25 - Repeat 1</t>
+  </si>
+  <si>
+    <t>06 Feb. 25 - Repeat 2</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>#A888B5</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\06FEB25_R1_EXAGGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\06FEB25_R2_EXAGGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>06FEB25_R1_EXAGGLOM_TANDEM_22-Feb-2025_21-36-25</t>
+  </si>
+  <si>
+    <t>06FEB25_R2_EXAGGLOM_TANDEM_23-Feb-2025_19-08-34</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>07 Feb. 25</t>
+  </si>
+  <si>
+    <t>Ex-Colaps</t>
+  </si>
+  <si>
+    <t>Hi-Aglom</t>
+  </si>
+  <si>
+    <t>#659287</t>
+  </si>
+  <si>
+    <t>07FEB25_EXCOLAPS_TANDEM_23-Feb-2025_20-44-35</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\07FEB25_EXCOLAPS_TANDEM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -513,18 +573,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="4"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="4" max="6" width="9.140625" style="4"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -540,31 +600,34 @@
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
@@ -572,28 +635,31 @@
       <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="F2" s="1">
+        <v>15</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
@@ -602,23 +668,26 @@
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="F3" s="1">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
@@ -631,23 +700,26 @@
       <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="F4" s="1">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -660,23 +732,26 @@
       <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="F5" s="1">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>41</v>
       </c>
-      <c r="J5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -689,23 +764,26 @@
       <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="F6" s="1">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>41</v>
       </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -718,28 +796,31 @@
       <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="F7" s="1">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>40</v>
       </c>
-      <c r="J7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>20</v>
@@ -747,81 +828,188 @@
       <c r="E8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="F8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>42</v>
       </c>
-      <c r="J8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="D9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="1">
+        <v>35</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="1">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1">
+        <v>15</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="b">
+      <c r="F12" s="1">
+        <v>15</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="4"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
+      <c r="B14" s="4"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/tandem_params_new.xlsx
+++ b/inputs/tandem_params_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hmdni\OneDrive\Documents\GitHub\odias\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C25131D-67A4-4CA3-82F4-D29D10DB3090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBE322F-3542-4644-A456-15C74F83B101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JUN24-AUG24-FEB25-All" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>fname</t>
   </si>
@@ -233,10 +233,61 @@
     <t>#659287</t>
   </si>
   <si>
-    <t>07FEB25_EXCOLAPS_TANDEM_23-Feb-2025_20-44-35</t>
-  </si>
-  <si>
     <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\07FEB25_EXCOLAPS_TANDEM</t>
+  </si>
+  <si>
+    <t>07FEB25_EXCOLAPS_TANDEM_13-Mar-2025_15-46-12</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\08FEB25_EXCOLAPS_TANDEM</t>
+  </si>
+  <si>
+    <t>08 Feb. 25</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>#A5B68D</t>
+  </si>
+  <si>
+    <t>11 Feb. 25</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\11FEB25_LOAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>11FEB25_LOAGLOM_TANDEM_14-Mar-2025_01-16-38</t>
+  </si>
+  <si>
+    <t>08FEB25_EXCOLAPS_TANDEM_14-Mar-2025_22-17-27</t>
+  </si>
+  <si>
+    <t>12FEB25_R1_EXAGLOM_TANDEM_14-Mar-2025_23-39-14</t>
+  </si>
+  <si>
+    <t>12 Feb. 25</t>
+  </si>
+  <si>
+    <t>#E6B2BA</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\12FEB25_R1_EXAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Publication\Experiment\Effective density\12FEB25_R2_EXAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>12FEB25_R2_EXAGLOM_TANDEM_15-Mar-2025_00-57-46</t>
+  </si>
+  <si>
+    <t>#FAD0C4</t>
   </si>
 </sst>
 </file>
@@ -573,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -627,7 +678,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
@@ -826,10 +877,10 @@
         <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F8" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>3</v>
@@ -913,10 +964,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>64</v>
@@ -944,12 +995,17 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>25</v>
+        <v>70</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="F12" s="1">
         <v>15</v>
@@ -958,41 +1014,116 @@
         <v>3</v>
       </c>
       <c r="H12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J12" t="s">
+        <v>68</v>
       </c>
       <c r="K12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="4"/>
-    </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="1">
+        <v>35</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>3</v>
+      </c>
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="1">
+        <v>35</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="5"/>
@@ -1008,6 +1139,15 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
